--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/LOUISIANA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/LOUISIANA_2011.xlsx
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C111">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C360">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C639">
